--- a/public/exports-60-250-with-coowners/20310413.xlsx
+++ b/public/exports-60-250-with-coowners/20310413.xlsx
@@ -3364,7 +3364,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311315219</t>
+          <t xml:space="preserve">311315218</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
